--- a/features_map.xlsx
+++ b/features_map.xlsx
@@ -196,390 +196,393 @@
     <t>bs_st_deferred_revenue_chg</t>
   </si>
   <si>
+    <t>bs_add_paid_in_cap_chg</t>
+  </si>
+  <si>
+    <t>net_debt_chg</t>
+  </si>
+  <si>
+    <t>net_debt_to_shrhldr_eqty_chg</t>
+  </si>
+  <si>
+    <t>cf_nt_csh_proc_pymt_debt_lvl</t>
+  </si>
+  <si>
+    <t>cf_pymt_debt_and_capital_lease_lvl</t>
+  </si>
+  <si>
+    <t>is_operating_expn_lvl</t>
+  </si>
+  <si>
+    <t>is_sg_and_a_expense_lvl</t>
+  </si>
+  <si>
+    <t>is_operating_expenses_r_and_d_lvl</t>
+  </si>
+  <si>
+    <t>bs_accts_rec_excl_notes_rec_lvl</t>
+  </si>
+  <si>
+    <t>bs_tot_non_cur_asset_lvl</t>
+  </si>
+  <si>
+    <t>bs_acct_payable_lvl</t>
+  </si>
+  <si>
+    <t>bs_tot_liab_lvl</t>
+  </si>
+  <si>
+    <t>bs_other_ins_res_to_shrhldr_eqy_lvl</t>
+  </si>
+  <si>
+    <t>cf_other_financing_act_excl_fx_chg</t>
+  </si>
+  <si>
+    <t>is_int_income_chg</t>
+  </si>
+  <si>
+    <t>is_inc_tax_exp_chg</t>
+  </si>
+  <si>
+    <t>is_min_noncontrol_interest_credits_chg</t>
+  </si>
+  <si>
+    <t>tot_debt_to_tot_eqy_lvl</t>
+  </si>
+  <si>
+    <t>ebitda.1_lvl</t>
+  </si>
+  <si>
+    <t>is_cogs_lvl</t>
+  </si>
+  <si>
+    <t>is_cog_and_services_sold_lvl</t>
+  </si>
+  <si>
+    <t>is_net_interest_expense_lvl</t>
+  </si>
+  <si>
+    <t>is_inc_tax_exp_lvl</t>
+  </si>
+  <si>
+    <t>is_avg_num_sh_for_eps_lvl</t>
+  </si>
+  <si>
+    <t>ebit_lvl</t>
+  </si>
+  <si>
+    <t>gross_margin_lvl</t>
+  </si>
+  <si>
+    <t>profit_margin.1_lvl</t>
+  </si>
+  <si>
+    <t>cash_conversion_cycle_lvl</t>
+  </si>
+  <si>
+    <t>ebitda_margin_chg</t>
+  </si>
+  <si>
+    <t>ebitda_margin.1_chg</t>
+  </si>
+  <si>
+    <t>tce_ratio_chg</t>
+  </si>
+  <si>
+    <t>ebitda_lvl</t>
+  </si>
+  <si>
+    <t>cash_flow_to_net_inc_lvl</t>
+  </si>
+  <si>
+    <t>cf_change_in_accounts_payable_lvl</t>
+  </si>
+  <si>
+    <t>cash_flow_to_net_inc.1_lvl</t>
+  </si>
+  <si>
+    <t>ebitda.2_lvl</t>
+  </si>
+  <si>
+    <t>cf_acct_rcv_unbilled_rev_chg</t>
+  </si>
+  <si>
+    <t>cf_acquis_fxd_and_intang_detailed_chg</t>
+  </si>
+  <si>
+    <t>cf_purchase_of_fixed_prod_assets_chg</t>
+  </si>
+  <si>
+    <t>cf_incr_invest_chg</t>
+  </si>
+  <si>
+    <t>cf_net_chng_cash_chg</t>
+  </si>
+  <si>
+    <t>cf_cap_expenditures_chg</t>
+  </si>
+  <si>
+    <t>bs_acct_note_rcv_chg</t>
+  </si>
+  <si>
+    <t>bs_other_current_liabs_detailed_chg</t>
+  </si>
+  <si>
+    <t>bs_sh_out.1_chg</t>
+  </si>
+  <si>
+    <t>bs_non_cur_liab_lvl</t>
+  </si>
+  <si>
+    <t>net_debt_lvl</t>
+  </si>
+  <si>
+    <t>cash_flow_to_net_inc_chg</t>
+  </si>
+  <si>
+    <t>cf_stock_based_compensation_chg</t>
+  </si>
+  <si>
+    <t>cf_change_in_accounts_payable_chg</t>
+  </si>
+  <si>
+    <t>is_other_operating_expenses_chg</t>
+  </si>
+  <si>
+    <t>bs_lt_borrow_chg</t>
+  </si>
+  <si>
+    <t>bs_non_cur_liab_chg</t>
+  </si>
+  <si>
+    <t>ebitda_per_sh_lvl</t>
+  </si>
+  <si>
+    <t>ebitda_margin_lvl</t>
+  </si>
+  <si>
+    <t>ev_to_ttm_ebitda_lvl</t>
+  </si>
+  <si>
+    <t>cf_cash_from_oper_lvl</t>
+  </si>
+  <si>
+    <t>cf_disposal_of_fixed_prod_assets_lvl</t>
+  </si>
+  <si>
+    <t>cf_cash_from_inv_act_lvl</t>
+  </si>
+  <si>
+    <t>ebitda_margin.1_lvl</t>
+  </si>
+  <si>
+    <t>is_sales_revenue_turnover_lvl</t>
+  </si>
+  <si>
+    <t>is_sales_and_services_revenues_lvl</t>
+  </si>
+  <si>
+    <t>is_oper_income_lvl</t>
+  </si>
+  <si>
+    <t>ebitda_margin.2_lvl</t>
+  </si>
+  <si>
+    <t>ebita_lvl</t>
+  </si>
+  <si>
+    <t>oper_margin_lvl</t>
+  </si>
+  <si>
+    <t>bs_tot_asset_lvl</t>
+  </si>
+  <si>
+    <t>bs_total_equity_lvl</t>
+  </si>
+  <si>
+    <t>ebitda_per_sh_chg</t>
+  </si>
+  <si>
+    <t>cf_non_cash_items_detailed_chg</t>
+  </si>
+  <si>
+    <t>ebita_chg</t>
+  </si>
+  <si>
+    <t>oper_margin_chg</t>
+  </si>
+  <si>
+    <t>cf_effect_foreign_exchanges_lvl</t>
+  </si>
+  <si>
+    <t>is_nonop_income_loss_lvl</t>
+  </si>
+  <si>
+    <t>is_other_nonop_income_loss_lvl</t>
+  </si>
+  <si>
+    <t>is_ni_including_minority_int_ratio_lvl</t>
+  </si>
+  <si>
+    <t>is_earn_for_common_lvl</t>
+  </si>
+  <si>
+    <t>revenue_per_sh_chg</t>
+  </si>
+  <si>
+    <t>cf_cash_from_fin_act_chg</t>
+  </si>
+  <si>
+    <t>cf_free_cash_flow_chg</t>
+  </si>
+  <si>
+    <t>cf_stock_based_compensation_lvl</t>
+  </si>
+  <si>
+    <t>cf_inc_dec_in_ot_op_ast_liab_detail_lvl</t>
+  </si>
+  <si>
+    <t>eps.1_lvl</t>
+  </si>
+  <si>
+    <t>diluted_eps_lvl</t>
+  </si>
+  <si>
+    <t>bs_other_assets_def_chrg_other_lvl</t>
+  </si>
+  <si>
+    <t>free_cash_flow_equity_chg</t>
+  </si>
+  <si>
+    <t>bs_c_and_ce_and_sti_detailed_chg</t>
+  </si>
+  <si>
+    <t>bs_cash_near_cash_item_chg</t>
+  </si>
+  <si>
+    <t>bs_other_current_assets_detailed_chg</t>
+  </si>
+  <si>
+    <t>bs_other_assets_def_chrg_other_chg</t>
+  </si>
+  <si>
+    <t>cf_depr_amort_lvl</t>
+  </si>
+  <si>
+    <t>is_other_operating_expenses_lvl</t>
+  </si>
+  <si>
+    <t>dil_eps_cont_ops_lvl</t>
+  </si>
+  <si>
+    <t>bs_c_and_ce_and_sti_detailed_lvl</t>
+  </si>
+  <si>
+    <t>bs_acct_payable_and_accruals_detailed_lvl</t>
+  </si>
+  <si>
+    <t>bs_pure_retained_earnings_lvl</t>
+  </si>
+  <si>
+    <t>eps_chg</t>
+  </si>
+  <si>
+    <t>cf_change_in_prepaid_assets_chg</t>
+  </si>
+  <si>
+    <t>pr_to_free_cash_flow_chg</t>
+  </si>
+  <si>
+    <t>is_operating_expn_chg</t>
+  </si>
+  <si>
+    <t>eps.1_chg</t>
+  </si>
+  <si>
+    <t>eps_cont_ops_chg</t>
+  </si>
+  <si>
+    <t>dil_eps_cont_ops_chg</t>
+  </si>
+  <si>
+    <t>bs_accum_depr_chg</t>
+  </si>
+  <si>
+    <t>cf_chng_non_cash_work_cap_lvl</t>
+  </si>
+  <si>
+    <t>eps_cont_ops_lvl</t>
+  </si>
+  <si>
+    <t>bs_other_intangible_assets_detailed_lvl</t>
+  </si>
+  <si>
+    <t>bs_st_capital_lease_obligations_lvl</t>
+  </si>
+  <si>
+    <t>bs_gross_fix_asset_chg</t>
+  </si>
+  <si>
+    <t>bs_disclosed_intangibles_chg</t>
+  </si>
+  <si>
+    <t>bs_st_capital_lease_obligations_chg</t>
+  </si>
+  <si>
+    <t>bs_lt_capital_lease_obligations_chg</t>
+  </si>
+  <si>
+    <t>bs_other_noncurrent_liabs_detailed_chg</t>
+  </si>
+  <si>
+    <t>bs_other_ins_res_to_shrhldr_eqy_chg</t>
+  </si>
+  <si>
+    <t>revenue_per_sh_lvl</t>
+  </si>
+  <si>
+    <t>is_extraord_items_and_acctg_chng_lvl</t>
+  </si>
+  <si>
+    <t>is_min_noncontrol_interest_credits_lvl</t>
+  </si>
+  <si>
+    <t>bs_invtry_in_progress_lvl</t>
+  </si>
+  <si>
+    <t>bs_other_current_assets_detailed_lvl</t>
+  </si>
+  <si>
+    <t>bs_disclosed_intangibles_lvl</t>
+  </si>
+  <si>
+    <t>bs_sh_cap_and_apic_lvl</t>
+  </si>
+  <si>
+    <t>cur_ratio_lvl</t>
+  </si>
+  <si>
+    <t>cf_disp_fxd_and_intangibles_detailed_lvl</t>
+  </si>
+  <si>
+    <t>cf_dvd_paid_lvl</t>
+  </si>
+  <si>
+    <t>bs_common_stock_lvl</t>
+  </si>
+  <si>
+    <t>cf_disp_fxd_and_intangibles_detailed_chg</t>
+  </si>
+  <si>
+    <t>bs_net_fix_asset_chg</t>
+  </si>
+  <si>
+    <t>bs_other_noncur_liabs_sub_detailed_chg</t>
+  </si>
+  <si>
     <t>bs_sh_cap_and_apic_chg</t>
   </si>
   <si>
-    <t>net_debt_chg</t>
-  </si>
-  <si>
-    <t>net_debt_to_shrhldr_eqty_chg</t>
-  </si>
-  <si>
-    <t>cf_nt_csh_proc_pymt_debt_lvl</t>
-  </si>
-  <si>
-    <t>cf_pymt_debt_and_capital_lease_lvl</t>
-  </si>
-  <si>
-    <t>is_operating_expn_lvl</t>
-  </si>
-  <si>
-    <t>is_sg_and_a_expense_lvl</t>
-  </si>
-  <si>
-    <t>is_operating_expenses_r_and_d_lvl</t>
-  </si>
-  <si>
-    <t>bs_accts_rec_excl_notes_rec_lvl</t>
-  </si>
-  <si>
-    <t>bs_tot_non_cur_asset_lvl</t>
-  </si>
-  <si>
-    <t>bs_acct_payable_lvl</t>
-  </si>
-  <si>
-    <t>bs_tot_liab_lvl</t>
-  </si>
-  <si>
-    <t>bs_other_ins_res_to_shrhldr_eqy_lvl</t>
-  </si>
-  <si>
-    <t>cf_other_financing_act_excl_fx_chg</t>
-  </si>
-  <si>
-    <t>is_int_income_chg</t>
-  </si>
-  <si>
-    <t>is_inc_tax_exp_chg</t>
-  </si>
-  <si>
-    <t>is_min_noncontrol_interest_credits_chg</t>
-  </si>
-  <si>
-    <t>tot_debt_to_tot_eqy_lvl</t>
-  </si>
-  <si>
-    <t>ebitda.1_lvl</t>
-  </si>
-  <si>
-    <t>is_cogs_lvl</t>
-  </si>
-  <si>
-    <t>is_cog_and_services_sold_lvl</t>
-  </si>
-  <si>
-    <t>is_net_interest_expense_lvl</t>
-  </si>
-  <si>
-    <t>is_inc_tax_exp_lvl</t>
-  </si>
-  <si>
-    <t>is_avg_num_sh_for_eps_lvl</t>
-  </si>
-  <si>
-    <t>ebit_lvl</t>
-  </si>
-  <si>
-    <t>gross_margin_lvl</t>
-  </si>
-  <si>
-    <t>profit_margin.1_lvl</t>
-  </si>
-  <si>
-    <t>cash_conversion_cycle_lvl</t>
-  </si>
-  <si>
-    <t>ebitda_margin_chg</t>
-  </si>
-  <si>
-    <t>ebitda_margin.1_chg</t>
-  </si>
-  <si>
-    <t>tce_ratio_chg</t>
-  </si>
-  <si>
-    <t>ebitda_lvl</t>
-  </si>
-  <si>
-    <t>cash_flow_to_net_inc_lvl</t>
-  </si>
-  <si>
-    <t>cf_change_in_accounts_payable_lvl</t>
-  </si>
-  <si>
-    <t>cash_flow_to_net_inc.1_lvl</t>
-  </si>
-  <si>
-    <t>ebitda.2_lvl</t>
-  </si>
-  <si>
-    <t>cf_acct_rcv_unbilled_rev_chg</t>
-  </si>
-  <si>
-    <t>cf_acquis_fxd_and_intang_detailed_chg</t>
-  </si>
-  <si>
-    <t>cf_purchase_of_fixed_prod_assets_chg</t>
-  </si>
-  <si>
-    <t>cf_incr_invest_chg</t>
-  </si>
-  <si>
-    <t>cf_net_chng_cash_chg</t>
-  </si>
-  <si>
-    <t>cf_cap_expenditures_chg</t>
-  </si>
-  <si>
-    <t>bs_acct_note_rcv_chg</t>
-  </si>
-  <si>
-    <t>bs_other_current_liabs_detailed_chg</t>
-  </si>
-  <si>
-    <t>bs_sh_out.1_chg</t>
-  </si>
-  <si>
-    <t>bs_non_cur_liab_lvl</t>
-  </si>
-  <si>
-    <t>net_debt_lvl</t>
-  </si>
-  <si>
-    <t>cash_flow_to_net_inc_chg</t>
-  </si>
-  <si>
-    <t>cf_stock_based_compensation_chg</t>
-  </si>
-  <si>
-    <t>cf_change_in_accounts_payable_chg</t>
-  </si>
-  <si>
-    <t>is_other_operating_expenses_chg</t>
-  </si>
-  <si>
-    <t>bs_lt_borrow_chg</t>
-  </si>
-  <si>
-    <t>bs_non_cur_liab_chg</t>
-  </si>
-  <si>
-    <t>ebitda_per_sh_lvl</t>
-  </si>
-  <si>
-    <t>ebitda_margin_lvl</t>
-  </si>
-  <si>
-    <t>ev_to_ttm_ebitda_lvl</t>
-  </si>
-  <si>
-    <t>cf_cash_from_oper_lvl</t>
-  </si>
-  <si>
-    <t>cf_disposal_of_fixed_prod_assets_lvl</t>
-  </si>
-  <si>
-    <t>cf_cash_from_inv_act_lvl</t>
-  </si>
-  <si>
-    <t>ebitda_margin.1_lvl</t>
-  </si>
-  <si>
-    <t>is_sales_revenue_turnover_lvl</t>
-  </si>
-  <si>
-    <t>is_sales_and_services_revenues_lvl</t>
-  </si>
-  <si>
-    <t>is_oper_income_lvl</t>
-  </si>
-  <si>
-    <t>ebitda_margin.2_lvl</t>
-  </si>
-  <si>
-    <t>ebita_lvl</t>
-  </si>
-  <si>
-    <t>oper_margin_lvl</t>
-  </si>
-  <si>
-    <t>bs_tot_asset_lvl</t>
-  </si>
-  <si>
-    <t>bs_total_equity_lvl</t>
-  </si>
-  <si>
-    <t>ebitda_per_sh_chg</t>
-  </si>
-  <si>
-    <t>cf_non_cash_items_detailed_chg</t>
-  </si>
-  <si>
-    <t>ebita_chg</t>
-  </si>
-  <si>
-    <t>oper_margin_chg</t>
-  </si>
-  <si>
-    <t>cf_effect_foreign_exchanges_lvl</t>
-  </si>
-  <si>
-    <t>is_nonop_income_loss_lvl</t>
-  </si>
-  <si>
-    <t>is_other_nonop_income_loss_lvl</t>
-  </si>
-  <si>
-    <t>is_ni_including_minority_int_ratio_lvl</t>
-  </si>
-  <si>
-    <t>is_earn_for_common_lvl</t>
-  </si>
-  <si>
-    <t>revenue_per_sh_chg</t>
-  </si>
-  <si>
-    <t>cf_cash_from_fin_act_chg</t>
-  </si>
-  <si>
-    <t>cf_free_cash_flow_chg</t>
-  </si>
-  <si>
-    <t>cf_stock_based_compensation_lvl</t>
-  </si>
-  <si>
-    <t>cf_inc_dec_in_ot_op_ast_liab_detail_lvl</t>
-  </si>
-  <si>
-    <t>eps.1_lvl</t>
-  </si>
-  <si>
-    <t>diluted_eps_lvl</t>
-  </si>
-  <si>
-    <t>bs_other_assets_def_chrg_other_lvl</t>
-  </si>
-  <si>
-    <t>free_cash_flow_equity_chg</t>
-  </si>
-  <si>
-    <t>bs_c_and_ce_and_sti_detailed_chg</t>
-  </si>
-  <si>
-    <t>bs_cash_near_cash_item_chg</t>
-  </si>
-  <si>
-    <t>bs_other_current_assets_detailed_chg</t>
-  </si>
-  <si>
-    <t>bs_other_assets_def_chrg_other_chg</t>
-  </si>
-  <si>
-    <t>cf_depr_amort_lvl</t>
-  </si>
-  <si>
-    <t>is_other_operating_expenses_lvl</t>
-  </si>
-  <si>
-    <t>dil_eps_cont_ops_lvl</t>
-  </si>
-  <si>
-    <t>bs_c_and_ce_and_sti_detailed_lvl</t>
-  </si>
-  <si>
-    <t>bs_acct_payable_and_accruals_detailed_lvl</t>
-  </si>
-  <si>
-    <t>bs_pure_retained_earnings_lvl</t>
-  </si>
-  <si>
-    <t>eps_chg</t>
-  </si>
-  <si>
-    <t>cf_change_in_prepaid_assets_chg</t>
-  </si>
-  <si>
-    <t>pr_to_free_cash_flow_chg</t>
-  </si>
-  <si>
-    <t>is_operating_expn_chg</t>
-  </si>
-  <si>
-    <t>eps.1_chg</t>
-  </si>
-  <si>
-    <t>eps_cont_ops_chg</t>
-  </si>
-  <si>
-    <t>dil_eps_cont_ops_chg</t>
-  </si>
-  <si>
-    <t>bs_accum_depr_chg</t>
-  </si>
-  <si>
-    <t>cf_chng_non_cash_work_cap_lvl</t>
-  </si>
-  <si>
-    <t>eps_cont_ops_lvl</t>
-  </si>
-  <si>
-    <t>bs_other_intangible_assets_detailed_lvl</t>
-  </si>
-  <si>
-    <t>bs_st_capital_lease_obligations_lvl</t>
-  </si>
-  <si>
-    <t>bs_gross_fix_asset_chg</t>
-  </si>
-  <si>
-    <t>bs_disclosed_intangibles_chg</t>
-  </si>
-  <si>
-    <t>bs_st_capital_lease_obligations_chg</t>
-  </si>
-  <si>
-    <t>bs_lt_capital_lease_obligations_chg</t>
-  </si>
-  <si>
-    <t>bs_other_noncurrent_liabs_detailed_chg</t>
-  </si>
-  <si>
-    <t>bs_other_ins_res_to_shrhldr_eqy_chg</t>
-  </si>
-  <si>
-    <t>revenue_per_sh_lvl</t>
-  </si>
-  <si>
-    <t>is_extraord_items_and_acctg_chng_lvl</t>
-  </si>
-  <si>
-    <t>is_min_noncontrol_interest_credits_lvl</t>
-  </si>
-  <si>
-    <t>bs_invtry_in_progress_lvl</t>
-  </si>
-  <si>
-    <t>bs_other_current_assets_detailed_lvl</t>
-  </si>
-  <si>
-    <t>bs_disclosed_intangibles_lvl</t>
-  </si>
-  <si>
-    <t>bs_sh_cap_and_apic_lvl</t>
-  </si>
-  <si>
-    <t>cur_ratio_lvl</t>
-  </si>
-  <si>
-    <t>cf_disp_fxd_and_intangibles_detailed_lvl</t>
-  </si>
-  <si>
-    <t>cf_dvd_paid_lvl</t>
-  </si>
-  <si>
-    <t>bs_common_stock_lvl</t>
-  </si>
-  <si>
-    <t>cf_disp_fxd_and_intangibles_detailed_chg</t>
-  </si>
-  <si>
-    <t>bs_net_fix_asset_chg</t>
-  </si>
-  <si>
-    <t>bs_other_noncur_liabs_sub_detailed_chg</t>
-  </si>
-  <si>
     <t>bs_minority_noncontrolling_interest_chg</t>
   </si>
   <si>
@@ -620,9 +623,6 @@
   </si>
   <si>
     <t>bs_tot_asset_chg</t>
-  </si>
-  <si>
-    <t>bs_add_paid_in_cap_chg</t>
   </si>
   <si>
     <t>ebitda_margin.2_chg</t>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -1676,7 +1676,7 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1706,7 +1706,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -1716,7 +1716,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -1726,7 +1726,7 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -1741,7 +1741,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -1766,7 +1766,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -1776,27 +1776,27 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1856,12 +1856,12 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -1886,7 +1886,7 @@
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -1901,12 +1901,12 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>196</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -1981,12 +1981,12 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -1996,7 +1996,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -2086,22 +2086,22 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>201</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>179</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -2201,12 +2201,12 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -2256,7 +2256,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3046,12 +3046,12 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:1">
